--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -59,6 +59,15 @@
     <t>ResotrePercent</t>
   </si>
   <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>ItemIdList</t>
+  </si>
+  <si>
+    <t>ItemQuantity</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -68,6 +77,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>小村杀鸡</t>
   </si>
   <si>
@@ -75,6 +87,15 @@
   </si>
   <si>
     <t>1000000000000</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>4008,4020</t>
+  </si>
+  <si>
+    <t>10,5</t>
   </si>
   <si>
     <t>比奇打骷髅</t>
@@ -133,7 +154,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +174,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -623,143 +651,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -771,9 +800,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1093,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1102,388 +1137,511 @@
     <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="3" customWidth="1"/>
     <col min="6" max="6" width="23.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.875" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
     <col min="9" max="11" width="12.5" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="12" max="12" width="14.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5" style="4" customWidth="1"/>
+    <col min="14" max="14" width="13.25" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="M4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:11">
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:11">
+        <v>16</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:11">
+        <v>22</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="M8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:11">
+      <c r="N8" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:11">
+    </row>
+    <row r="10" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:11">
+        <v>31</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="5:11">
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" customHeight="1" spans="5:11">
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" customHeight="1" spans="5:11">
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" customHeight="1" spans="5:11">
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" customHeight="1" spans="5:5">
-      <c r="E16" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="5:5">
-      <c r="E18" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="5:5">
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customHeight="1" spans="5:5">
-      <c r="E21" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="5:5">
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" customHeight="1" spans="5:5">
-      <c r="E24" s="7"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:6">
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:6">
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:6">
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" customHeight="1" spans="6:6">
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" customHeight="1" spans="6:6">
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="6:6">
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:6">
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:6">
-      <c r="F34" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="5:13">
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="11"/>
+    </row>
+    <row r="13" customHeight="1" spans="5:13">
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="11"/>
+    </row>
+    <row r="14" customHeight="1" spans="5:13">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="11"/>
+    </row>
+    <row r="15" customHeight="1" spans="5:13">
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16" customHeight="1" spans="5:13">
+      <c r="E16" s="8"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" customHeight="1" spans="13:13">
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" customHeight="1" spans="5:13">
+      <c r="E18" s="8"/>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" customHeight="1" spans="13:13">
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" customHeight="1" spans="5:13">
+      <c r="E20" s="8"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" customHeight="1" spans="5:13">
+      <c r="E21" s="8"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" customHeight="1" spans="13:13">
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" customHeight="1" spans="5:13">
+      <c r="E23" s="8"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" customHeight="1" spans="5:13">
+      <c r="E24" s="8"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" customHeight="1" spans="13:13">
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" customHeight="1" spans="13:13">
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:13">
+      <c r="F27" s="8"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="6:13">
+      <c r="F28" s="8"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" customHeight="1" spans="6:13">
+      <c r="F29" s="8"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" customHeight="1" spans="6:13">
+      <c r="F30" s="8"/>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" customHeight="1" spans="6:13">
+      <c r="F31" s="8"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" customHeight="1" spans="6:13">
+      <c r="F32" s="8"/>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" customHeight="1" spans="6:13">
+      <c r="F33" s="8"/>
+      <c r="M33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="6:13">
+      <c r="F34" s="8"/>
+      <c r="M34" s="1"/>
     </row>
     <row r="35" customHeight="1" spans="6:6">
-      <c r="F35" s="7"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" customHeight="1" spans="6:6">
-      <c r="F36" s="7"/>
+      <c r="F36" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5 E3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -38,27 +38,6 @@
     <t>MapName</t>
   </si>
   <si>
-    <t>Attr</t>
-  </si>
-  <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>DamageIncrea</t>
-  </si>
-  <si>
-    <t>DamageResist</t>
-  </si>
-  <si>
-    <t>CritRateResist</t>
-  </si>
-  <si>
-    <t>ResotrePercent</t>
-  </si>
-  <si>
     <t>ItemType</t>
   </si>
   <si>
@@ -83,12 +62,6 @@
     <t>小村杀鸡</t>
   </si>
   <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>1000000000000</t>
-  </si>
-  <si>
     <t>5,5</t>
   </si>
   <si>
@@ -101,58 +74,27 @@
     <t>比奇打骷髅</t>
   </si>
   <si>
-    <t>2000000</t>
-  </si>
-  <si>
-    <t>2000000000000</t>
-  </si>
-  <si>
     <t>矿洞打僵尸</t>
   </si>
   <si>
-    <t>3000000</t>
-  </si>
-  <si>
-    <t>3000000000000</t>
-  </si>
-  <si>
     <t>山谷杀蛇</t>
   </si>
   <si>
-    <t>4000000</t>
-  </si>
-  <si>
-    <t>4000000000000</t>
-  </si>
-  <si>
     <t>蜈蚣洞</t>
   </si>
   <si>
-    <t>5000000</t>
-  </si>
-  <si>
-    <t>5000000000000</t>
-  </si>
-  <si>
     <t>猪洞烧猪</t>
-  </si>
-  <si>
-    <t>6000000</t>
-  </si>
-  <si>
-    <t>6000000000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -781,32 +723,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1128,520 +1056,260 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
-    <col min="9" max="11" width="12.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.25" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.25" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="M1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:7">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:14">
+        <v>9</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:7">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:14">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:7">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:14">
+        <v>14</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:7">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:14">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:7">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:14">
+        <v>16</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:7">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="5:13">
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="11"/>
-    </row>
-    <row r="13" customHeight="1" spans="5:13">
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="11"/>
-    </row>
-    <row r="14" customHeight="1" spans="5:13">
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="11"/>
-    </row>
-    <row r="15" customHeight="1" spans="5:13">
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="11"/>
-    </row>
-    <row r="16" customHeight="1" spans="5:13">
-      <c r="E16" s="8"/>
-      <c r="M16" s="11"/>
-    </row>
-    <row r="17" customHeight="1" spans="13:13">
-      <c r="M17" s="11"/>
-    </row>
-    <row r="18" customHeight="1" spans="5:13">
-      <c r="E18" s="8"/>
-      <c r="M18" s="11"/>
-    </row>
-    <row r="19" customHeight="1" spans="13:13">
-      <c r="M19" s="11"/>
-    </row>
-    <row r="20" customHeight="1" spans="5:13">
-      <c r="E20" s="8"/>
-      <c r="M20" s="11"/>
-    </row>
-    <row r="21" customHeight="1" spans="5:13">
-      <c r="E21" s="8"/>
-      <c r="M21" s="11"/>
-    </row>
-    <row r="22" customHeight="1" spans="13:13">
-      <c r="M22" s="11"/>
-    </row>
-    <row r="23" customHeight="1" spans="5:13">
-      <c r="E23" s="8"/>
-      <c r="M23" s="11"/>
-    </row>
-    <row r="24" customHeight="1" spans="5:13">
-      <c r="E24" s="8"/>
-      <c r="M24" s="11"/>
-    </row>
-    <row r="25" customHeight="1" spans="13:13">
-      <c r="M25" s="11"/>
-    </row>
-    <row r="26" customHeight="1" spans="13:13">
-      <c r="M26" s="11"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:13">
-      <c r="F27" s="8"/>
-      <c r="M27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:13">
-      <c r="F28" s="8"/>
-      <c r="M28" s="11"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:13">
-      <c r="F29" s="8"/>
-      <c r="M29" s="11"/>
-    </row>
-    <row r="30" customHeight="1" spans="6:13">
-      <c r="F30" s="8"/>
-      <c r="M30" s="11"/>
-    </row>
-    <row r="31" customHeight="1" spans="6:13">
-      <c r="F31" s="8"/>
-      <c r="M31" s="11"/>
-    </row>
-    <row r="32" customHeight="1" spans="6:13">
-      <c r="F32" s="8"/>
-      <c r="M32" s="11"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:13">
-      <c r="F33" s="8"/>
-      <c r="M33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:13">
-      <c r="F34" s="8"/>
-      <c r="M34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="6:6">
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" customHeight="1" spans="6:6">
-      <c r="F36" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="6:6">
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" customHeight="1" spans="6:6">
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" customHeight="1" spans="6:6">
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="6:6">
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="6:6">
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="6:6">
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="6:6">
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="6:6">
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="6:6">
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="6:6">
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="6:6">
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="6:6">
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="6:6">
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="6:6">
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="6:6">
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:6">
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="6:6">
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="6:6">
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="6:6">
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="6:6">
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="6:6">
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="6:6">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="6:6">
+      <c r="F34" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -77,10 +77,16 @@
     <t>矿洞打僵尸</t>
   </si>
   <si>
+    <t>10,6</t>
+  </si>
+  <si>
     <t>山谷杀蛇</t>
   </si>
   <si>
-    <t>蜈蚣洞</t>
+    <t>地下砍蜈蚣</t>
+  </si>
+  <si>
+    <t>10,7</t>
   </si>
   <si>
     <t>猪洞烧猪</t>
@@ -1062,7 +1068,7 @@
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="13.25" style="1" customWidth="1"/>
@@ -1184,7 +1190,7 @@
         <v>11</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:7">
@@ -1192,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>10</v>
@@ -1201,7 +1207,7 @@
         <v>11</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:7">
@@ -1209,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>10</v>
@@ -1218,7 +1224,7 @@
         <v>11</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:7">
@@ -1226,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>10</v>
@@ -1235,7 +1241,7 @@
         <v>11</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="6:6">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -59,37 +59,55 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>小村杀鸡</t>
-  </si>
-  <si>
-    <t>5,5</t>
-  </si>
-  <si>
-    <t>4008,4020</t>
-  </si>
-  <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>比奇打骷髅</t>
+    <t>银杏杀鸡</t>
+  </si>
+  <si>
+    <t>5,5,5,9,5,9,5,5</t>
+  </si>
+  <si>
+    <t>4008,4020,4014,4003,4004,4013,4011,4019</t>
+  </si>
+  <si>
+    <t>10,5,100,500,50,25,5,1</t>
+  </si>
+  <si>
+    <t>村外砍鹿</t>
+  </si>
+  <si>
+    <t>大战食人花</t>
+  </si>
+  <si>
+    <t>10,6,200,600,60,30,10,2</t>
+  </si>
+  <si>
+    <t>洞穴战骷髅</t>
+  </si>
+  <si>
+    <t>山谷捕蛇</t>
+  </si>
+  <si>
+    <t>10,7,300,700,70,35,15,3</t>
   </si>
   <si>
     <t>矿洞打僵尸</t>
   </si>
   <si>
-    <t>10,6</t>
-  </si>
-  <si>
-    <t>山谷杀蛇</t>
-  </si>
-  <si>
-    <t>地下砍蜈蚣</t>
-  </si>
-  <si>
-    <t>10,7</t>
+    <t>沃玛砍教主</t>
+  </si>
+  <si>
+    <t>10,8,400,800,80,40,20,4</t>
+  </si>
+  <si>
+    <t>大战触龙神</t>
   </si>
   <si>
     <t>猪洞烧猪</t>
+  </si>
+  <si>
+    <t>10,9,500,900,90,45,25,5</t>
+  </si>
+  <si>
+    <t>祖玛生死间</t>
   </si>
 </sst>
 </file>
@@ -1062,16 +1080,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="29.875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1244,32 +1262,93 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="6:6">
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="6:6">
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="6:6">
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="6:6">
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="6:6">
+    <row r="12" customHeight="1" spans="3:7">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:7">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:7">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:7">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="6:9">
       <c r="F16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="6:6">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="6:9">
       <c r="F17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="6:6">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="6:9">
       <c r="F18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="6:6">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="6:9">
       <c r="F19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="6:6">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" customHeight="1" spans="6:9">
       <c r="F20" s="6"/>
+      <c r="I20" s="1"/>
     </row>
     <row r="21" customHeight="1" spans="6:6">
       <c r="F21" s="6"/>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -62,13 +62,13 @@
     <t>银杏杀鸡</t>
   </si>
   <si>
-    <t>5,5,5,9,5,9,5,5</t>
-  </si>
-  <si>
-    <t>4008,4020,4014,4003,4004,4013,4011,4019</t>
-  </si>
-  <si>
-    <t>10,5,100,500,50,25,5,1</t>
+    <t>5,9,5,9,15,5,5,5</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020</t>
+  </si>
+  <si>
+    <t>10,500,50,25,100,5,1,5</t>
   </si>
   <si>
     <t>村外砍鹿</t>
@@ -77,7 +77,7 @@
     <t>大战食人花</t>
   </si>
   <si>
-    <t>10,6,200,600,60,30,10,2</t>
+    <t>10,600,60,30,200,10,2,6</t>
   </si>
   <si>
     <t>洞穴战骷髅</t>
@@ -86,7 +86,7 @@
     <t>山谷捕蛇</t>
   </si>
   <si>
-    <t>10,7,300,700,70,35,15,3</t>
+    <t>10,700,70,35,300,15,3,7</t>
   </si>
   <si>
     <t>矿洞打僵尸</t>
@@ -95,7 +95,7 @@
     <t>沃玛砍教主</t>
   </si>
   <si>
-    <t>10,8,400,800,80,40,20,4</t>
+    <t>10,800,80,40,400,20,4,8</t>
   </si>
   <si>
     <t>大战触龙神</t>
@@ -104,7 +104,7 @@
     <t>猪洞烧猪</t>
   </si>
   <si>
-    <t>10,9,500,900,90,45,25,5</t>
+    <t>10,900,90,45,500,25,5,9</t>
   </si>
   <si>
     <t>祖玛生死间</t>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -62,7 +62,7 @@
     <t>银杏杀鸡</t>
   </si>
   <si>
-    <t>5,9,5,9,15,5,5,5</t>
+    <t>5,9,5,9,15,5,5,15</t>
   </si>
   <si>
     <t>4008,4003,4004,4013,4014,4011,4019,4020</t>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>银杏杀鸡</t>
+    <t>小村杀鸡</t>
   </si>
   <si>
     <t>5,9,5,9,15,5,5,15</t>
@@ -80,34 +80,34 @@
     <t>10,600,60,30,200,10,2,6</t>
   </si>
   <si>
-    <t>洞穴战骷髅</t>
-  </si>
-  <si>
-    <t>山谷捕蛇</t>
+    <t>大战骷髅</t>
+  </si>
+  <si>
+    <t>大战毒蛇</t>
   </si>
   <si>
     <t>10,700,70,35,300,15,3,7</t>
   </si>
   <si>
-    <t>矿洞打僵尸</t>
-  </si>
-  <si>
-    <t>沃玛砍教主</t>
+    <t>大战僵尸</t>
+  </si>
+  <si>
+    <t>大战恶魔</t>
   </si>
   <si>
     <t>10,800,80,40,400,20,4,8</t>
   </si>
   <si>
-    <t>大战触龙神</t>
-  </si>
-  <si>
-    <t>猪洞烧猪</t>
+    <t>大战蜈蚣</t>
+  </si>
+  <si>
+    <t>大战野猪</t>
   </si>
   <si>
     <t>10,900,90,45,500,25,5,9</t>
   </si>
   <si>
-    <t>祖玛生死间</t>
+    <t>大战邪魔</t>
   </si>
 </sst>
 </file>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -108,6 +108,15 @@
   </si>
   <si>
     <t>大战邪魔</t>
+  </si>
+  <si>
+    <t>大战红月</t>
+  </si>
+  <si>
+    <t>10,1000,100,50,600,30,6,10</t>
+  </si>
+  <si>
+    <t>大战魔龙</t>
   </si>
 </sst>
 </file>
@@ -1330,13 +1339,39 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="6:9">
-      <c r="F16" s="6"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="6:9">
-      <c r="F17" s="6"/>
-      <c r="I17" s="1"/>
+    <row r="16" customHeight="1" spans="3:7">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:7">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" customHeight="1" spans="6:9">
       <c r="F18" s="6"/>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>大战魔龙</t>
+  </si>
+  <si>
+    <t>大战雷炎</t>
+  </si>
+  <si>
+    <t>10,1100,110,55,700,35,7,11</t>
+  </si>
+  <si>
+    <t>大战雪域</t>
   </si>
 </sst>
 </file>
@@ -1373,13 +1382,39 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="6:9">
-      <c r="F18" s="6"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="6:9">
-      <c r="F19" s="6"/>
-      <c r="I19" s="1"/>
+    <row r="18" customHeight="1" spans="3:7">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:7">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="20" customHeight="1" spans="6:9">
       <c r="F20" s="6"/>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -126,6 +126,21 @@
   </si>
   <si>
     <t>大战雪域</t>
+  </si>
+  <si>
+    <t>大战狐月</t>
+  </si>
+  <si>
+    <t>5,9,5,9,15,5,5,15,5</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026</t>
+  </si>
+  <si>
+    <t>10,1200,120,60,800,40,8,12,5</t>
+  </si>
+  <si>
+    <t>大战石原</t>
   </si>
 </sst>
 </file>
@@ -1098,15 +1113,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="32.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="29.875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -1416,12 +1431,39 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="6:9">
-      <c r="F20" s="6"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="6:6">
-      <c r="F21" s="6"/>
+    <row r="20" customHeight="1" spans="3:7">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:7">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="6:6">
       <c r="F22" s="6"/>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>大战雪域</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>大战狐月</t>
@@ -1431,38 +1434,50 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:7">
+    <row r="20" customHeight="1" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:7">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:7">
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="6:6">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>大战雪域</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>大战狐月</t>
@@ -1434,50 +1431,38 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:7">
-      <c r="A20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>32</v>
-      </c>
+    <row r="20" customHeight="1" spans="3:7">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>32</v>
-      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:7">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="6:6">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>大战石原</t>
+  </si>
+  <si>
+    <t>卧龙山庄</t>
+  </si>
+  <si>
+    <t>万蝙魔窟</t>
+  </si>
+  <si>
+    <t>骨魔仙洞</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1123,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
@@ -1465,14 +1474,56 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="6:6">
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="6:6">
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="6:6">
-      <c r="F24" s="6"/>
+    <row r="22" customHeight="1" spans="3:7">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:7">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:7">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="25" customHeight="1" spans="6:6">
       <c r="F25" s="6"/>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -146,10 +146,25 @@
     <t>卧龙山庄</t>
   </si>
   <si>
+    <t>5,9,5,9,15,5,5,15,5,3,5</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,1011,4112</t>
+  </si>
+  <si>
+    <t>10,1300,130,65,900,45,9,12,6,1,5</t>
+  </si>
+  <si>
     <t>万蝙魔窟</t>
   </si>
   <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,2011,4112</t>
+  </si>
+  <si>
     <t>骨魔仙洞</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4112</t>
   </si>
 </sst>
 </file>
@@ -1129,8 +1144,8 @@
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.8333333333333" style="3" customWidth="1"/>
     <col min="7" max="7" width="29.875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -1482,13 +1497,13 @@
         <v>37</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:7">
@@ -1496,16 +1511,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="F23" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:7">
@@ -1513,16 +1528,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="6:6">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -149,7 +149,7 @@
     <t>5,9,5,9,15,5,5,15,5,3,5</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,1011,4112</t>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,1011,4035</t>
   </si>
   <si>
     <t>10,1300,130,65,900,45,9,12,6,1,5</t>
@@ -158,13 +158,13 @@
     <t>万蝙魔窟</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,2011,4112</t>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,2011,4035</t>
   </si>
   <si>
     <t>骨魔仙洞</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4112</t>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4035</t>
   </si>
 </sst>
 </file>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -165,6 +165,60 @@
   </si>
   <si>
     <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4035</t>
+  </si>
+  <si>
+    <t>金域秘境</t>
+  </si>
+  <si>
+    <t>5,9,5,9,15,5,5,15,5,4,5</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,28,4039</t>
+  </si>
+  <si>
+    <t>10,1400,140,70,1000,50,10,13,7,2,5</t>
+  </si>
+  <si>
+    <t>魂骨</t>
+  </si>
+  <si>
+    <t>木域秘境</t>
+  </si>
+  <si>
+    <t>5,9,5,9,15,5,5,15,5,5,5</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4025,4039</t>
+  </si>
+  <si>
+    <t>10,1400,140,70,1000,50,10,13,7,1,5</t>
+  </si>
+  <si>
+    <t>金宠</t>
+  </si>
+  <si>
+    <t>水域秘境</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,36,4039</t>
+  </si>
+  <si>
+    <t>10,1400,140,70,1000,50,10,13,7,50,5</t>
+  </si>
+  <si>
+    <t>宝石</t>
+  </si>
+  <si>
+    <t>火域秘境</t>
+  </si>
+  <si>
+    <t>10,1400,140,70,1000,50,10,13,7,75,5</t>
+  </si>
+  <si>
+    <t>土域秘境</t>
+  </si>
+  <si>
+    <t>10,1400,140,70,1000,50,10,13,7,100,5</t>
   </si>
 </sst>
 </file>
@@ -1137,8 +1191,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
@@ -1540,20 +1594,105 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="6:6">
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:6">
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:6">
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:6">
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:6">
-      <c r="F29" s="6"/>
+    <row r="25" customHeight="1" spans="3:8">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:8">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="6:6">
       <c r="F30" s="6"/>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -203,22 +203,22 @@
     <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,36,4039</t>
   </si>
   <si>
+    <t>10,1400,140,70,1000,50,10,13,7,30,5</t>
+  </si>
+  <si>
+    <t>宝石</t>
+  </si>
+  <si>
+    <t>火域秘境</t>
+  </si>
+  <si>
+    <t>10,1400,140,70,1000,50,10,13,7,40,5</t>
+  </si>
+  <si>
+    <t>土域秘境</t>
+  </si>
+  <si>
     <t>10,1400,140,70,1000,50,10,13,7,50,5</t>
-  </si>
-  <si>
-    <t>宝石</t>
-  </si>
-  <si>
-    <t>火域秘境</t>
-  </si>
-  <si>
-    <t>10,1400,140,70,1000,50,10,13,7,75,5</t>
-  </si>
-  <si>
-    <t>土域秘境</t>
-  </si>
-  <si>
-    <t>10,1400,140,70,1000,50,10,13,7,100,5</t>
   </si>
 </sst>
 </file>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +38,9 @@
     <t>MapName</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>ItemType</t>
   </si>
   <si>
@@ -219,6 +222,24 @@
   </si>
   <si>
     <t>10,1400,140,70,1000,50,10,13,7,50,5</t>
+  </si>
+  <si>
+    <t>挑战仙鸡</t>
+  </si>
+  <si>
+    <t>10,1500,150,75,1100,50,11,14,8,50,5</t>
+  </si>
+  <si>
+    <t>挑战仙鹿</t>
+  </si>
+  <si>
+    <t>挑战仙花</t>
+  </si>
+  <si>
+    <t>挑战仙魂</t>
+  </si>
+  <si>
+    <t>挑战仙蛇</t>
   </si>
 </sst>
 </file>
@@ -1191,30 +1212,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.8333333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="29.875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="13.4166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="42.8333333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="29.875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1226,18 +1248,21 @@
       <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1245,473 +1270,745 @@
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:7">
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
         <v>10</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:7">
+      <c r="H6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:7">
+      <c r="H7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:7">
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:7">
+      <c r="G9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:7">
+      <c r="G10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:7">
+      <c r="G11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:7">
+      <c r="G12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:7">
+      <c r="G13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:7">
+      <c r="G14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:7">
+      <c r="G15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:7">
+      <c r="G16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:7">
+      <c r="G17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:7">
+      <c r="G18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:11">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:7">
+      <c r="G19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="7" t="s">
         <v>33</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:7">
+      <c r="H20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:7">
+      <c r="H21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="7" t="s">
         <v>38</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:7">
+      <c r="H22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:11">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:7">
+      <c r="K23" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:11">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:8">
+        <v>39</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:11">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="7" t="s">
         <v>46</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:8">
+      <c r="I25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:11">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="7" t="s">
         <v>51</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:8">
+      <c r="I26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:11">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:8">
+      <c r="I27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K27" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:8">
+      <c r="K28" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:11">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>46</v>
+        <v>62</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="6:6">
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="6:6">
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="6:6">
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:6">
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:6">
-      <c r="F34" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K29" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:11">
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:11">
+      <c r="C31" s="1">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K31" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:11">
+      <c r="C32" s="1">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K32" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:11">
+      <c r="C33" s="1">
+        <v>27</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K33" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
+      <c r="C34" s="1">
+        <v>28</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K34" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
+      <c r="C35" s="1">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K35" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:11">
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -227,19 +227,46 @@
     <t>挑战仙鸡</t>
   </si>
   <si>
-    <t>10,1500,150,75,1100,50,11,14,8,50,5</t>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,1011,4038</t>
+  </si>
+  <si>
+    <t>10,1500,150,75,1100,50,11,14,10,1,8</t>
+  </si>
+  <si>
+    <t>时装精华*1</t>
   </si>
   <si>
     <t>挑战仙鹿</t>
   </si>
   <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,2011,4038</t>
+  </si>
+  <si>
+    <t>超级书页*1</t>
+  </si>
+  <si>
     <t>挑战仙花</t>
   </si>
   <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4038</t>
+  </si>
+  <si>
+    <t>11技能自选</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>挑战仙魂</t>
   </si>
   <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4034,4038</t>
+  </si>
+  <si>
     <t>挑战仙蛇</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4112,4038</t>
   </si>
 </sst>
 </file>
@@ -1883,16 +1910,16 @@
         <v>2</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K31" s="2">
         <v>13</v>
@@ -1903,112 +1930,123 @@
         <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="K32" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:11">
+    <row r="33" customHeight="1" spans="1:11">
       <c r="C33" s="1">
         <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K33" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:11">
+    <row r="34" customHeight="1" spans="1:11">
+      <c r="A34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="C34" s="1">
         <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K34" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:11">
+    <row r="35" customHeight="1" spans="1:11">
+      <c r="A35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="C35" s="1">
         <v>29</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K35" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:11">
+    <row r="36" customHeight="1" spans="1:11">
       <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -233,40 +233,40 @@
     <t>10,1500,150,75,1100,50,11,14,10,1,8</t>
   </si>
   <si>
+    <t>11技能自选</t>
+  </si>
+  <si>
+    <t>挑战仙鹿</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,2011,4038</t>
+  </si>
+  <si>
+    <t>挑战仙花</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4038</t>
+  </si>
+  <si>
+    <t>挑战仙魂</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4034,4038</t>
+  </si>
+  <si>
     <t>时装精华*1</t>
   </si>
   <si>
-    <t>挑战仙鹿</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,2011,4038</t>
+    <t>挑战仙蛇</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4112,4038</t>
   </si>
   <si>
     <t>超级书页*1</t>
   </si>
   <si>
-    <t>挑战仙花</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,3011,4038</t>
-  </si>
-  <si>
-    <t>11技能自选</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>挑战仙魂</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4034,4038</t>
-  </si>
-  <si>
-    <t>挑战仙蛇</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4112,4038</t>
+    <t>挑战仙傀</t>
   </si>
 </sst>
 </file>
@@ -1945,18 +1945,18 @@
         <v>66</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K32" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:11">
+    <row r="33" customHeight="1" spans="3:11">
       <c r="C33" s="1">
         <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -1965,30 +1965,24 @@
         <v>39</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>66</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K33" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:11">
-      <c r="A34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>74</v>
-      </c>
+    <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="1">
         <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -1997,30 +1991,24 @@
         <v>39</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>66</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K34" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:11">
-      <c r="A35" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>74</v>
-      </c>
+    <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="1">
         <v>29</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -2029,20 +2017,43 @@
         <v>39</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>66</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K35" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:11">
-      <c r="F36" s="6"/>
+    <row r="36" customHeight="1" spans="3:11">
+      <c r="C36" s="1">
+        <v>30</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K36" s="2">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -1988,7 +1988,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>73</v>
@@ -2014,7 +2014,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>76</v>
@@ -2040,7 +2040,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>73</v>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -233,7 +233,7 @@
     <t>10,1500,150,75,1100,50,11,14,10,1,8</t>
   </si>
   <si>
-    <t>11技能自选</t>
+    <t>11技能自选，混沌精华</t>
   </si>
   <si>
     <t>挑战仙鹿</t>
@@ -254,7 +254,7 @@
     <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4034,4038</t>
   </si>
   <si>
-    <t>时装精华*1</t>
+    <t>时装精华*1，混沌精华</t>
   </si>
   <si>
     <t>挑战仙蛇</t>
@@ -263,10 +263,40 @@
     <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4112,4038</t>
   </si>
   <si>
-    <t>超级书页*1</t>
+    <t>超级书页*1，混沌精华</t>
   </si>
   <si>
     <t>挑战仙傀</t>
+  </si>
+  <si>
+    <t>挑战仙鹰</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4112,4037</t>
+  </si>
+  <si>
+    <t>10,1500,150,75,1200,50,11,14,10,1,8</t>
+  </si>
+  <si>
+    <t>超级书页*1，永恒精华</t>
+  </si>
+  <si>
+    <t>挑战仙虫</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4034,4037</t>
+  </si>
+  <si>
+    <t>时装精华*1，永恒精华</t>
+  </si>
+  <si>
+    <t>挑战仙猪</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,41,4037</t>
+  </si>
+  <si>
+    <t>神器自选*1，永恒精华</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1250,7 +1280,8 @@
     <col min="6" max="6" width="21.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="42.8333333333333" style="3" customWidth="1"/>
     <col min="8" max="8" width="29.875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="19.9166666666667" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
@@ -2053,6 +2084,75 @@
       </c>
       <c r="K36" s="2">
         <v>13</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
+      <c r="C37" s="1">
+        <v>31</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
+      <c r="C38" s="1">
+        <v>32</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
+      <c r="C39" s="1">
+        <v>33</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="90">
   <si>
     <t>ID</t>
   </si>
@@ -272,10 +272,10 @@
     <t>挑战仙鹰</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4112,4037</t>
-  </si>
-  <si>
-    <t>10,1500,150,75,1200,50,11,14,10,1,8</t>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4037,4112</t>
+  </si>
+  <si>
+    <t>10,1500,150,75,1200,50,11,14,10,8,1</t>
   </si>
   <si>
     <t>超级书页*1，永恒精华</t>
@@ -284,7 +284,7 @@
     <t>挑战仙虫</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4034,4037</t>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4037,4034</t>
   </si>
   <si>
     <t>时装精华*1，永恒精华</t>
@@ -293,7 +293,10 @@
     <t>挑战仙猪</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,41,4037</t>
+    <t>5,9,5,9,15,5,5,15,5,5,4</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4026,4037,41</t>
   </si>
   <si>
     <t>神器自选*1，永恒精华</t>
@@ -2143,16 +2146,16 @@
         <v>2</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>81</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -300,6 +300,33 @@
   </si>
   <si>
     <t>神器自选*1，永恒精华</t>
+  </si>
+  <si>
+    <t>挑战邪魔</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4037,4024</t>
+  </si>
+  <si>
+    <t>10,1500,150,75,1200,50,11,14,10,8,2</t>
+  </si>
+  <si>
+    <t>红色魂心*2，永恒精华</t>
+  </si>
+  <si>
+    <t>挑战魔蛛</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4037,4034</t>
+  </si>
+  <si>
+    <t>挑战魔龙</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,47</t>
+  </si>
+  <si>
+    <t>极神器自选*1，虚无精华</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2158,6 +2185,75 @@
         <v>89</v>
       </c>
     </row>
+    <row r="40" customHeight="1" spans="3:11">
+      <c r="C40" s="1">
+        <v>34</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:11">
+      <c r="C41" s="1">
+        <v>35</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:11">
+      <c r="C42" s="1">
+        <v>36</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -327,6 +327,33 @@
   </si>
   <si>
     <t>极神器自选*1，虚无精华</t>
+  </si>
+  <si>
+    <t>挑战雷域</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,44</t>
+  </si>
+  <si>
+    <t>极特自选*1，虚无精华</t>
+  </si>
+  <si>
+    <t>挑战冰域</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,28</t>
+  </si>
+  <si>
+    <t>魂骨自选*2，虚无精华</t>
+  </si>
+  <si>
+    <t>挑战狐仙</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,4025</t>
+  </si>
+  <si>
+    <t>金色魂心*1，虚无精华</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2254,6 +2281,75 @@
         <v>98</v>
       </c>
     </row>
+    <row r="43" customHeight="1" spans="3:11">
+      <c r="C43" s="1">
+        <v>37</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:11">
+      <c r="C44" s="1">
+        <v>38</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:11">
+      <c r="C45" s="1">
+        <v>39</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -354,6 +354,30 @@
   </si>
   <si>
     <t>金色魂心*1，虚无精华</t>
+  </si>
+  <si>
+    <t>仙界废墟</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,4034</t>
+  </si>
+  <si>
+    <t>时装精华*1，虚无精华</t>
+  </si>
+  <si>
+    <t>凌霄仙山</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,4112</t>
+  </si>
+  <si>
+    <t>超级书页*1，虚无精华</t>
+  </si>
+  <si>
+    <t>白虎秘境</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,48</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1350,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2350,6 +2374,75 @@
         <v>107</v>
       </c>
     </row>
+    <row r="46" customHeight="1" spans="3:11">
+      <c r="C46" s="1">
+        <v>40</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:11">
+      <c r="C47" s="1">
+        <v>41</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:11">
+      <c r="C48" s="1">
+        <v>42</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="120">
   <si>
     <t>ID</t>
   </si>
@@ -378,6 +383,18 @@
   </si>
   <si>
     <t>4008,4003,4004,4013,4014,4011,4019,4020,4038,4046,48</t>
+  </si>
+  <si>
+    <t>青龙秘境</t>
+  </si>
+  <si>
+    <t>朱雀秘境</t>
+  </si>
+  <si>
+    <t>玄武秘境</t>
+  </si>
+  <si>
+    <t>极戒*1，虚无精华</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2443,6 +2460,75 @@
         <v>98</v>
       </c>
     </row>
+    <row r="49" customHeight="1" spans="3:9">
+      <c r="C49" s="1">
+        <v>43</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:9">
+      <c r="C50" s="1">
+        <v>44</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:9">
+      <c r="C51" s="1">
+        <v>45</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
